--- a/nadzor.xlsx
+++ b/nadzor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://zespolszkolzawodowychnr5-my.sharepoint.com/personal/admin_zsz5_edupage_org/Documents/zastepstwa-main/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maciejnajwer/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="559" documentId="8_{A0206B6A-DBF6-424B-ADF1-111B2E61D922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9ADC5153-34CD-7640-91EB-445619629BC4}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0A119FCC-C6E3-7843-BB56-9F957CE1FC94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="600" windowWidth="34200" windowHeight="19500" activeTab="1" xr2:uid="{21B880B6-615E-B441-9859-DA562C2886D8}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="34200" windowHeight="19580" xr2:uid="{21B880B6-615E-B441-9859-DA562C2886D8}"/>
   </bookViews>
   <sheets>
     <sheet name="grafik dyżurów" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="104">
   <si>
     <t>poniedziałek</t>
   </si>
@@ -356,6 +356,18 @@
   </si>
   <si>
     <t>wewnetrzny numer</t>
+  </si>
+  <si>
+    <t>13.04-17.04.2026</t>
+  </si>
+  <si>
+    <t>20.04-25.04.2026</t>
+  </si>
+  <si>
+    <t>Maciej Najwer/od 10:00Marzena Filusz</t>
+  </si>
+  <si>
+    <t>27.04-1.05.2026</t>
   </si>
 </sst>
 </file>
@@ -744,6 +756,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="45" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="45"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -756,17 +774,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="45"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1102,17 +1114,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61CC7B51-F6FE-8D4D-8449-0994E5374E58}">
-  <dimension ref="A1:I83"/>
+  <dimension ref="A1:I95"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.6640625" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="7" width="31" customWidth="1"/>
+    <col min="3" max="5" width="31" customWidth="1"/>
+    <col min="6" max="6" width="33.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="31" customWidth="1"/>
     <col min="8" max="9" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="45" t="s">
         <v>5</v>
       </c>
       <c r="B1" s="19" t="s">
@@ -1135,7 +1149,7 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="52" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="52"/>
+      <c r="A2" s="45"/>
       <c r="B2" s="21" t="s">
         <v>7</v>
       </c>
@@ -1156,7 +1170,7 @@
       </c>
     </row>
     <row r="3" spans="1:9" ht="52" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="52"/>
+      <c r="A3" s="45"/>
       <c r="B3" s="23" t="s">
         <v>11</v>
       </c>
@@ -1184,7 +1198,7 @@
       <c r="G4" s="7"/>
     </row>
     <row r="5" spans="1:9" ht="36" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="49" t="s">
+      <c r="A5" s="46" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="15" t="s">
@@ -1207,7 +1221,7 @@
       </c>
     </row>
     <row r="6" spans="1:9" ht="36" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="49"/>
+      <c r="A6" s="46"/>
       <c r="B6" s="4" t="s">
         <v>7</v>
       </c>
@@ -1226,13 +1240,13 @@
       <c r="G6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H6" s="45" t="s">
+      <c r="H6" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="I6" s="46"/>
+      <c r="I6" s="48"/>
     </row>
     <row r="7" spans="1:9" ht="36" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="49"/>
+      <c r="A7" s="46"/>
       <c r="B7" s="5" t="s">
         <v>11</v>
       </c>
@@ -1249,8 +1263,8 @@
       <c r="G7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="45"/>
-      <c r="I7" s="46"/>
+      <c r="H7" s="47"/>
+      <c r="I7" s="48"/>
     </row>
     <row r="8" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="18"/>
@@ -1262,7 +1276,7 @@
       <c r="G8" s="7"/>
     </row>
     <row r="9" spans="1:9" ht="36" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="49" t="s">
+      <c r="A9" s="46" t="s">
         <v>16</v>
       </c>
       <c r="B9" s="15" t="s">
@@ -1287,7 +1301,7 @@
       <c r="I9" s="3"/>
     </row>
     <row r="10" spans="1:9" ht="36" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="49"/>
+      <c r="A10" s="46"/>
       <c r="B10" s="4" t="s">
         <v>7</v>
       </c>
@@ -1306,13 +1320,13 @@
       <c r="G10" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="H10" s="45" t="s">
+      <c r="H10" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="I10" s="47"/>
+      <c r="I10" s="49"/>
     </row>
     <row r="11" spans="1:9" ht="36" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="49"/>
+      <c r="A11" s="46"/>
       <c r="B11" s="5" t="s">
         <v>11</v>
       </c>
@@ -1329,8 +1343,8 @@
       <c r="G11" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H11" s="48"/>
-      <c r="I11" s="47"/>
+      <c r="H11" s="50"/>
+      <c r="I11" s="49"/>
     </row>
     <row r="12" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="18"/>
@@ -1342,7 +1356,7 @@
       <c r="G12" s="7"/>
     </row>
     <row r="13" spans="1:9" ht="36" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="49" t="s">
+      <c r="A13" s="46" t="s">
         <v>18</v>
       </c>
       <c r="B13" s="15" t="s">
@@ -1367,7 +1381,7 @@
       <c r="I13" s="3"/>
     </row>
     <row r="14" spans="1:9" ht="36" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="49"/>
+      <c r="A14" s="46"/>
       <c r="B14" s="4" t="s">
         <v>7</v>
       </c>
@@ -1384,13 +1398,13 @@
       <c r="G14" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="45" t="s">
+      <c r="H14" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="I14" s="47"/>
+      <c r="I14" s="49"/>
     </row>
     <row r="15" spans="1:9" ht="36" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="49"/>
+      <c r="A15" s="46"/>
       <c r="B15" s="5" t="s">
         <v>11</v>
       </c>
@@ -1405,8 +1419,8 @@
       <c r="G15" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H15" s="48"/>
-      <c r="I15" s="47"/>
+      <c r="H15" s="50"/>
+      <c r="I15" s="49"/>
     </row>
     <row r="16" spans="1:9" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="18"/>
@@ -1418,7 +1432,7 @@
       <c r="G16" s="7"/>
     </row>
     <row r="17" spans="1:9" ht="35" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="49" t="s">
+      <c r="A17" s="46" t="s">
         <v>19</v>
       </c>
       <c r="B17" s="15" t="s">
@@ -1441,7 +1455,7 @@
       </c>
     </row>
     <row r="18" spans="1:9" ht="35" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="49"/>
+      <c r="A18" s="46"/>
       <c r="B18" s="4" t="s">
         <v>7</v>
       </c>
@@ -1460,13 +1474,13 @@
       <c r="G18" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H18" s="45" t="s">
+      <c r="H18" s="47" t="s">
         <v>21</v>
       </c>
-      <c r="I18" s="47"/>
+      <c r="I18" s="49"/>
     </row>
     <row r="19" spans="1:9" ht="35" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="49"/>
+      <c r="A19" s="46"/>
       <c r="B19" s="5" t="s">
         <v>11</v>
       </c>
@@ -1483,8 +1497,8 @@
       <c r="G19" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H19" s="48"/>
-      <c r="I19" s="47"/>
+      <c r="H19" s="50"/>
+      <c r="I19" s="49"/>
     </row>
     <row r="20" spans="1:9" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" s="18"/>
@@ -1496,7 +1510,7 @@
       <c r="G20" s="7"/>
     </row>
     <row r="21" spans="1:9" ht="35" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="49" t="s">
+      <c r="A21" s="46" t="s">
         <v>23</v>
       </c>
       <c r="B21" s="15" t="s">
@@ -1519,7 +1533,7 @@
       </c>
     </row>
     <row r="22" spans="1:9" ht="35" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="49"/>
+      <c r="A22" s="46"/>
       <c r="B22" s="4" t="s">
         <v>7</v>
       </c>
@@ -1538,13 +1552,13 @@
       <c r="G22" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H22" s="50" t="s">
+      <c r="H22" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="I22" s="51"/>
+      <c r="I22" s="52"/>
     </row>
     <row r="23" spans="1:9" ht="35" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="49"/>
+      <c r="A23" s="46"/>
       <c r="B23" s="5" t="s">
         <v>11</v>
       </c>
@@ -1561,8 +1575,8 @@
       <c r="G23" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H23" s="50"/>
-      <c r="I23" s="51"/>
+      <c r="H23" s="51"/>
+      <c r="I23" s="52"/>
     </row>
     <row r="24" spans="1:9" ht="18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" s="18"/>
@@ -1574,7 +1588,7 @@
       <c r="G24" s="7"/>
     </row>
     <row r="25" spans="1:9" ht="36" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="49" t="s">
+      <c r="A25" s="46" t="s">
         <v>24</v>
       </c>
       <c r="B25" s="15" t="s">
@@ -1597,7 +1611,7 @@
       </c>
     </row>
     <row r="26" spans="1:9" ht="36" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="49"/>
+      <c r="A26" s="46"/>
       <c r="B26" s="4" t="s">
         <v>7</v>
       </c>
@@ -1618,7 +1632,7 @@
       </c>
     </row>
     <row r="27" spans="1:9" ht="36" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="49"/>
+      <c r="A27" s="46"/>
       <c r="B27" s="5" t="s">
         <v>11</v>
       </c>
@@ -1646,7 +1660,7 @@
       <c r="G28" s="7"/>
     </row>
     <row r="29" spans="1:9" ht="44" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="49" t="s">
+      <c r="A29" s="46" t="s">
         <v>26</v>
       </c>
       <c r="B29" s="15" t="s">
@@ -1669,7 +1683,7 @@
       </c>
     </row>
     <row r="30" spans="1:9" ht="44" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="49"/>
+      <c r="A30" s="46"/>
       <c r="B30" s="4" t="s">
         <v>7</v>
       </c>
@@ -1688,7 +1702,7 @@
       </c>
     </row>
     <row r="31" spans="1:9" ht="44" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="49"/>
+      <c r="A31" s="46"/>
       <c r="B31" s="5" t="s">
         <v>11</v>
       </c>
@@ -2624,18 +2638,223 @@
         <v>13</v>
       </c>
     </row>
+    <row r="84" spans="1:7" ht="18" x14ac:dyDescent="0.2">
+      <c r="A84" s="18"/>
+      <c r="B84" s="18"/>
+      <c r="C84" s="7"/>
+      <c r="D84" s="7"/>
+      <c r="E84" s="7"/>
+      <c r="F84" s="7"/>
+      <c r="G84" s="7"/>
+    </row>
+    <row r="85" spans="1:7" ht="18" x14ac:dyDescent="0.2">
+      <c r="A85" s="44" t="s">
+        <v>100</v>
+      </c>
+      <c r="B85" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C85" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D85" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E85" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F85" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G85" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" ht="65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="44"/>
+      <c r="B86" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="44"/>
+      <c r="B87" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E87" s="7"/>
+      <c r="F87" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" ht="18" x14ac:dyDescent="0.2">
+      <c r="A88" s="18"/>
+      <c r="B88" s="18"/>
+      <c r="C88" s="7"/>
+      <c r="D88" s="7"/>
+      <c r="E88" s="7"/>
+      <c r="F88" s="7"/>
+      <c r="G88" s="7"/>
+    </row>
+    <row r="89" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="44" t="s">
+        <v>101</v>
+      </c>
+      <c r="B89" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E89" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F89" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G89" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" ht="65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="44"/>
+      <c r="B90" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" ht="65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="44"/>
+      <c r="B91" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E91" s="7"/>
+      <c r="F91" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" ht="18" x14ac:dyDescent="0.2">
+      <c r="A92" s="18"/>
+      <c r="B92" s="18"/>
+      <c r="C92" s="7"/>
+      <c r="D92" s="7"/>
+      <c r="E92" s="7"/>
+      <c r="F92" s="7"/>
+      <c r="G92" s="7"/>
+    </row>
+    <row r="93" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="44" t="s">
+        <v>103</v>
+      </c>
+      <c r="B93" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D93" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E93" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F93" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G93" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" ht="65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="44"/>
+      <c r="B94" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G94" s="7"/>
+    </row>
+    <row r="95" spans="1:7" ht="65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="44"/>
+      <c r="B95" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E95" s="7"/>
+      <c r="F95" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G95" s="7"/>
+    </row>
   </sheetData>
-  <mergeCells count="26">
-    <mergeCell ref="A53:A55"/>
-    <mergeCell ref="A49:A51"/>
-    <mergeCell ref="A45:A47"/>
-    <mergeCell ref="A41:A43"/>
-    <mergeCell ref="A37:A39"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="A17:A19"/>
+  <mergeCells count="29">
+    <mergeCell ref="A85:A87"/>
+    <mergeCell ref="A89:A91"/>
+    <mergeCell ref="A93:A95"/>
     <mergeCell ref="A73:A75"/>
     <mergeCell ref="A77:A79"/>
     <mergeCell ref="A81:A83"/>
@@ -2652,6 +2871,16 @@
     <mergeCell ref="A57:A59"/>
     <mergeCell ref="A61:A63"/>
     <mergeCell ref="A65:A67"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="A53:A55"/>
+    <mergeCell ref="A49:A51"/>
+    <mergeCell ref="A45:A47"/>
+    <mergeCell ref="A41:A43"/>
+    <mergeCell ref="A37:A39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
@@ -2972,7 +3201,7 @@
       <c r="F14" s="33"/>
       <c r="G14" s="35"/>
     </row>
-    <row r="15" spans="1:7" ht="300" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" ht="325" x14ac:dyDescent="0.2">
       <c r="A15" s="37" t="s">
         <v>51</v>
       </c>

--- a/nadzor.xlsx
+++ b/nadzor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maciejnajwer/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://zespolszkolzawodowychnr5-my.sharepoint.com/personal/admin_zsz5_edupage_org/Documents/nowe zastepstwa/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0A119FCC-C6E3-7843-BB56-9F957CE1FC94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="565" documentId="8_{A0206B6A-DBF6-424B-ADF1-111B2E61D922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{26A482FB-BF65-C442-8DC2-D9FC4F07CBAA}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="34200" windowHeight="19580" xr2:uid="{21B880B6-615E-B441-9859-DA562C2886D8}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="34200" windowHeight="19500" xr2:uid="{21B880B6-615E-B441-9859-DA562C2886D8}"/>
   </bookViews>
   <sheets>
     <sheet name="grafik dyżurów" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="101">
   <si>
     <t>poniedziałek</t>
   </si>
@@ -358,16 +358,7 @@
     <t>wewnetrzny numer</t>
   </si>
   <si>
-    <t>13.04-17.04.2026</t>
-  </si>
-  <si>
-    <t>20.04-25.04.2026</t>
-  </si>
-  <si>
-    <t>Maciej Najwer/od 10:00Marzena Filusz</t>
-  </si>
-  <si>
-    <t>27.04-1.05.2026</t>
+    <t>4.05.2026-8.05.2026</t>
   </si>
 </sst>
 </file>
@@ -435,7 +426,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -514,8 +505,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC1F0C8"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF000000"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -618,11 +621,37 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -779,6 +808,21 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1114,14 +1158,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61CC7B51-F6FE-8D4D-8449-0994E5374E58}">
-  <dimension ref="A1:I95"/>
+  <dimension ref="A1:I91"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.6640625" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="31" customWidth="1"/>
-    <col min="6" max="6" width="33.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="31" customWidth="1"/>
+    <col min="3" max="7" width="31" customWidth="1"/>
     <col min="8" max="9" width="22" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2647,7 +2689,7 @@
       <c r="F84" s="7"/>
       <c r="G84" s="7"/>
     </row>
-    <row r="85" spans="1:7" ht="18" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:7" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="44" t="s">
         <v>100</v>
       </c>
@@ -2670,43 +2712,43 @@
         <v>4</v>
       </c>
     </row>
-    <row r="86" spans="1:7" ht="65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:7" ht="52" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="44"/>
       <c r="B86" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C86" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F86" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="G86" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" ht="65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C86" s="53" t="s">
+        <v>8</v>
+      </c>
+      <c r="D86" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="E86" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="F86" s="54" t="s">
+        <v>8</v>
+      </c>
+      <c r="G86" s="54" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="52" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="44"/>
       <c r="B87" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C87" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E87" s="7"/>
-      <c r="F87" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G87" s="2" t="s">
+      <c r="C87" s="55" t="s">
+        <v>10</v>
+      </c>
+      <c r="D87" s="56" t="s">
+        <v>12</v>
+      </c>
+      <c r="E87" s="57"/>
+      <c r="F87" s="56" t="s">
+        <v>12</v>
+      </c>
+      <c r="G87" s="56" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2719,9 +2761,9 @@
       <c r="F88" s="7"/>
       <c r="G88" s="7"/>
     </row>
-    <row r="89" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:7" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="44" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="B89" s="15" t="s">
         <v>6</v>
@@ -2742,119 +2784,50 @@
         <v>4</v>
       </c>
     </row>
-    <row r="90" spans="1:7" ht="65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:7" ht="52" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="44"/>
       <c r="B90" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C90" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F90" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G90" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" ht="65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C90" s="53" t="s">
+        <v>8</v>
+      </c>
+      <c r="D90" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="E90" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="F90" s="54" t="s">
+        <v>8</v>
+      </c>
+      <c r="G90" s="54" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" ht="52" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="44"/>
       <c r="B91" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C91" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E91" s="7"/>
-      <c r="F91" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G91" s="2" t="s">
+      <c r="C91" s="55" t="s">
+        <v>10</v>
+      </c>
+      <c r="D91" s="56" t="s">
+        <v>12</v>
+      </c>
+      <c r="E91" s="57"/>
+      <c r="F91" s="56" t="s">
+        <v>12</v>
+      </c>
+      <c r="G91" s="56" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="92" spans="1:7" ht="18" x14ac:dyDescent="0.2">
-      <c r="A92" s="18"/>
-      <c r="B92" s="18"/>
-      <c r="C92" s="7"/>
-      <c r="D92" s="7"/>
-      <c r="E92" s="7"/>
-      <c r="F92" s="7"/>
-      <c r="G92" s="7"/>
-    </row>
-    <row r="93" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="44" t="s">
-        <v>103</v>
-      </c>
-      <c r="B93" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="C93" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D93" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="E93" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="F93" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="G93" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" ht="65" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="44"/>
-      <c r="B94" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F94" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G94" s="7"/>
-    </row>
-    <row r="95" spans="1:7" ht="65" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="44"/>
-      <c r="B95" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E95" s="7"/>
-      <c r="F95" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G95" s="7"/>
-    </row>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="28">
     <mergeCell ref="A85:A87"/>
     <mergeCell ref="A89:A91"/>
-    <mergeCell ref="A93:A95"/>
     <mergeCell ref="A73:A75"/>
     <mergeCell ref="A77:A79"/>
     <mergeCell ref="A81:A83"/>
@@ -3201,7 +3174,7 @@
       <c r="F14" s="33"/>
       <c r="G14" s="35"/>
     </row>
-    <row r="15" spans="1:7" ht="325" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" ht="300" x14ac:dyDescent="0.2">
       <c r="A15" s="37" t="s">
         <v>51</v>
       </c>
